--- a/pregenerated_results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
+++ b/pregenerated_results/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,10 +537,10 @@
         <v>0.012</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.014</v>
+        <v>-0.013</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.002</v>
+        <v>-0.0009999999999999992</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -564,10 +564,10 @@
         <v>0.046</v>
       </c>
       <c r="D5" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>0.035</v>
+        <v>0.036</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.024</v>
+        <v>-0.128</v>
       </c>
       <c r="D7" t="n">
-        <v>0.027</v>
+        <v>0.018</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.002999999999999999</v>
+        <v>0.11</v>
       </c>
       <c r="F7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.046</v>
+        <v>-0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.002</v>
+        <v>-0.005</v>
       </c>
       <c r="E8" t="n">
-        <v>0.044</v>
+        <v>-0.005</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.107</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.001</v>
+        <v>0.042</v>
       </c>
       <c r="E9" t="n">
-        <v>0.008</v>
+        <v>0.065</v>
       </c>
       <c r="F9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.074</v>
+        <v>0.034</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.042</v>
+        <v>-0.008</v>
       </c>
       <c r="E10" t="n">
-        <v>0.03199999999999999</v>
+        <v>0.026</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,16 +723,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.034</v>
+        <v>0.392</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.008</v>
+        <v>0.03</v>
       </c>
       <c r="E11" t="n">
-        <v>0.026</v>
+        <v>0.362</v>
       </c>
       <c r="F11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -753,10 +753,10 @@
         <v>0.023</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="E12" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.007</v>
+        <v>0.041</v>
       </c>
       <c r="D13" t="n">
-        <v>0.025</v>
+        <v>0.037</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.018</v>
+        <v>0.004000000000000004</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,13 +804,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.041</v>
+        <v>-0.054</v>
       </c>
       <c r="D14" t="n">
-        <v>0.038</v>
+        <v>-0.027</v>
       </c>
       <c r="E14" t="n">
-        <v>0.003000000000000003</v>
+        <v>0.027</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.005</v>
+        <v>-0.008</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.013</v>
+        <v>-0.002</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.008</v>
+        <v>0.006</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.032</v>
+        <v>-0.401</v>
       </c>
       <c r="D16" t="n">
-        <v>0.03</v>
+        <v>-0.038</v>
       </c>
       <c r="E16" t="n">
-        <v>0.002000000000000002</v>
+        <v>0.363</v>
       </c>
       <c r="F16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.014</v>
+        <v>0.007</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.003</v>
+        <v>0.025</v>
       </c>
       <c r="E17" t="n">
-        <v>0.011</v>
+        <v>-0.018</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0</v>
+        <v>0.005</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.004</v>
+        <v>-0.012</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.004</v>
+        <v>-0.007</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.008</v>
+        <v>-0.113</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.001</v>
+        <v>-0.049</v>
       </c>
       <c r="E19" t="n">
-        <v>0.007</v>
+        <v>0.064</v>
       </c>
       <c r="F19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,16 +966,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.077</v>
+        <v>-0.143</v>
       </c>
       <c r="D20" t="n">
-        <v>0.031</v>
+        <v>-0.042</v>
       </c>
       <c r="E20" t="n">
-        <v>0.046</v>
+        <v>0.101</v>
       </c>
       <c r="F20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.019</v>
+        <v>-0.024</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.023</v>
+        <v>0.027</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.004</v>
+        <v>-0.002999999999999999</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.113</v>
+        <v>0.032</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.05</v>
+        <v>0.032</v>
       </c>
       <c r="E22" t="n">
-        <v>0.063</v>
+        <v>0</v>
       </c>
       <c r="F22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,16 +1047,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.197</v>
+        <v>0.022</v>
       </c>
       <c r="D23" t="n">
-        <v>0.065</v>
+        <v>0.015</v>
       </c>
       <c r="E23" t="n">
-        <v>0.132</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,13 +1074,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.143</v>
+        <v>0.227</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.042</v>
+        <v>0.024</v>
       </c>
       <c r="E24" t="n">
-        <v>0.101</v>
+        <v>0.203</v>
       </c>
       <c r="F24" t="b">
         <v>0</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.054</v>
+        <v>0.046</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.027</v>
+        <v>-0.002</v>
       </c>
       <c r="E25" t="n">
-        <v>0.027</v>
+        <v>0.044</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,16 +1128,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-0.128</v>
+        <v>0.077</v>
       </c>
       <c r="D26" t="n">
-        <v>0.019</v>
+        <v>0.031</v>
       </c>
       <c r="E26" t="n">
-        <v>0.109</v>
+        <v>0.046</v>
       </c>
       <c r="F26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,16 +1155,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.227</v>
+        <v>-0.014</v>
       </c>
       <c r="D27" t="n">
-        <v>0.022</v>
+        <v>-0.003</v>
       </c>
       <c r="E27" t="n">
-        <v>0.205</v>
+        <v>0.011</v>
       </c>
       <c r="F27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.392</v>
+        <v>0.197</v>
       </c>
       <c r="D28" t="n">
-        <v>0.03</v>
+        <v>0.067</v>
       </c>
       <c r="E28" t="n">
-        <v>0.362</v>
+        <v>0.13</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,16 +1209,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.401</v>
+        <v>-0.074</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.038</v>
+        <v>-0.042</v>
       </c>
       <c r="E29" t="n">
-        <v>0.363</v>
+        <v>0.03199999999999999</v>
       </c>
       <c r="F29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,16 +1236,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.107</v>
+        <v>-0.041</v>
       </c>
       <c r="D30" t="n">
-        <v>0.042</v>
+        <v>-0.012</v>
       </c>
       <c r="E30" t="n">
-        <v>0.065</v>
+        <v>0.029</v>
       </c>
       <c r="F30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.041</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.013</v>
+        <v>-0.002</v>
       </c>
       <c r="E31" t="n">
-        <v>0.028</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.066</v>
+        <v>-0.019</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.057</v>
+        <v>-0.024</v>
       </c>
       <c r="E32" t="n">
-        <v>0.009000000000000001</v>
+        <v>-0.005000000000000001</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1308,7 +1308,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1317,18 +1317,45 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.022</v>
+        <v>-0.066</v>
       </c>
       <c r="D33" t="n">
-        <v>0.015</v>
+        <v>-0.057</v>
       </c>
       <c r="E33" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F33" t="b">
         <v>1</v>
       </c>
       <c r="G33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>baseline_manager_efficacy</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.082</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-0.024</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="F34" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1388,22 +1415,22 @@
         <v>7220</v>
       </c>
       <c r="B2" t="n">
-        <v>7094.386718944053</v>
+        <v>7095.308361203054</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9957648995493169</v>
+        <v>0.9956602987071268</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1325095691671194</v>
+        <v>0.132000111260347</v>
       </c>
       <c r="E2" t="n">
-        <v>1.678870188120527</v>
+        <v>1.66716426106409</v>
       </c>
       <c r="F2" t="n">
-        <v>1.124267686541995</v>
+        <v>1.124233559763564</v>
       </c>
       <c r="G2" t="n">
-        <v>1.678043421071839</v>
+        <v>1.665574299117989</v>
       </c>
     </row>
   </sheetData>
@@ -1464,19 +1491,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.749032162934507</v>
+        <v>1.748744200678082</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09972330619000462</v>
+        <v>0.09972246735547846</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553578074382837</v>
+        <v>1.553291756211873</v>
       </c>
       <c r="E2" t="n">
-        <v>1.944486251486176</v>
+        <v>1.944196645144292</v>
       </c>
       <c r="F2" t="n">
-        <v>7.237657289135669e-69</v>
+        <v>7.595130829723318e-69</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1516,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02962572488141944</v>
+        <v>0.02958633974415715</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01822264113750337</v>
+        <v>0.01822177522012755</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.00608999545128517</v>
+        <v>-0.006127683421677257</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06534144521412405</v>
+        <v>0.06530036290999156</v>
       </c>
       <c r="F3" t="n">
-        <v>0.103999741677488</v>
+        <v>0.1044440307699907</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,19 +1541,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09776307597911855</v>
+        <v>0.09784011424187256</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04954667549874944</v>
+        <v>0.04951895669896678</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0006533764478765247</v>
+        <v>0.0007847425598992291</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1948727755103606</v>
+        <v>0.1948954859238459</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04847835276759649</v>
+        <v>0.04817615306008689</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1566,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.01287593631557939</v>
+        <v>-0.01273797200940386</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03341847660338249</v>
+        <v>0.03343233284250818</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.07837494687640349</v>
+        <v>-0.07826414029987552</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05262307424524471</v>
+        <v>0.0527881962810678</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7000196553266508</v>
+        <v>0.7031976288909354</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1591,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04934458162077574</v>
+        <v>0.04927628124940898</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03238690772777992</v>
+        <v>0.03239456843861483</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.01413259109629485</v>
+        <v>-0.01421590618499402</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1128217543378463</v>
+        <v>0.112768468683812</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1276095198106726</v>
+        <v>0.1282277489991762</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1616,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01045597826565334</v>
+        <v>0.01047785258090152</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0325231034746707</v>
+        <v>0.03252233317855409</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.05328813321017072</v>
+        <v>-0.05326474914227655</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07420008974147739</v>
+        <v>0.07422045430407959</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478361600842367</v>
+        <v>0.7473208240704075</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1641,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0643481418368291</v>
+        <v>0.06433271843302675</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03290386814872377</v>
+        <v>0.03291080729184542</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0001422546867241165</v>
+        <v>-0.0001712785611284739</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1288385383603823</v>
+        <v>0.128836715427182</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05050750165873732</v>
+        <v>0.0506114447635788</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,19 +1666,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02877420831517306</v>
+        <v>0.02865140490375859</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03191215009447935</v>
+        <v>0.03191029283342593</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.03377245653924295</v>
+        <v>-0.03389161978588283</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09132087316958908</v>
+        <v>0.0911944295934</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3672325279422067</v>
+        <v>0.3692530175492087</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1691,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.001018984209322789</v>
+        <v>-0.0009794214476962217</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05063846000222123</v>
+        <v>0.05063414819939269</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1002685420462485</v>
+        <v>-0.1002205283063695</v>
       </c>
       <c r="E10" t="n">
-        <v>0.09823057362760287</v>
+        <v>0.09826168541097707</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9839454655173238</v>
+        <v>0.9845674006463209</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1716,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01931633161945882</v>
+        <v>0.01946826154009439</v>
       </c>
       <c r="C11" t="n">
-        <v>0.05194329107217199</v>
+        <v>0.05194685720438133</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.08249064812047921</v>
+        <v>-0.08234570769053806</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1211233113593969</v>
+        <v>0.1212822307707268</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7099870626555926</v>
+        <v>0.7078295534163974</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1741,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0677289801249665</v>
+        <v>0.06785609067849595</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0516355781888226</v>
+        <v>0.051639055827471</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.03347489344602775</v>
+        <v>-0.03335459893900042</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1689328536959608</v>
+        <v>0.1690667802959923</v>
       </c>
       <c r="F12" t="n">
-        <v>0.18963057959976</v>
+        <v>0.1888307512048419</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1766,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03988129614662066</v>
+        <v>0.04035183396023324</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0517181369470819</v>
+        <v>0.05171295167094475</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.06148438961717016</v>
+        <v>-0.06100368884907888</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1412469819104115</v>
+        <v>0.1417073567695454</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4406311499162627</v>
+        <v>0.4352118346691917</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1791,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01333034569364382</v>
+        <v>0.01360432138726293</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0532208559389335</v>
+        <v>0.05321733263316387</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0909806151730605</v>
+        <v>-0.09069973392702638</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1176413065603481</v>
+        <v>0.1179083767015522</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8022221889070273</v>
+        <v>0.7982311147396423</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1816,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05372608150388213</v>
+        <v>0.05405252017528392</v>
       </c>
       <c r="C15" t="n">
-        <v>0.05226717408728838</v>
+        <v>0.05226735188844171</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.04871569728088826</v>
+        <v>-0.0483896070933434</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1561678602886525</v>
+        <v>0.1564946474439112</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3039909897906238</v>
+        <v>0.3010639142436627</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1841,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04075528353732606</v>
+        <v>0.04086477158037354</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05309570953627994</v>
+        <v>0.05309945880834852</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.06331039488738252</v>
+        <v>-0.06320825528255769</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1448209619620346</v>
+        <v>0.1449377984433048</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4427358660730105</v>
+        <v>0.4415435960896872</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1866,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.01088254976687354</v>
+        <v>0.01102820644228609</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05158432471739419</v>
+        <v>0.05158345722977697</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.09022086884603836</v>
+        <v>-0.09007351192613902</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1119859683797854</v>
+        <v>0.1121299248107112</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8329136341204481</v>
+        <v>0.8307081155011059</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1891,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.02863194690982666</v>
+        <v>0.02900589471309427</v>
       </c>
       <c r="C18" t="n">
-        <v>0.04992876705012337</v>
+        <v>0.04992506750994714</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.06922663830090531</v>
+        <v>-0.06884543953213293</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1264905321205586</v>
+        <v>0.1268572289583215</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5663360387177497</v>
+        <v>0.5612481417346349</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1916,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.009518215481816599</v>
+        <v>0.009706893816720184</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0518916769429116</v>
+        <v>0.05188944681346105</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.09218760242367767</v>
+        <v>-0.09199455311537014</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1112240333873109</v>
+        <v>0.1114083407488105</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8544647937149347</v>
+        <v>0.851606731564822</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1941,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.01322088667279006</v>
+        <v>-0.01294184623909357</v>
       </c>
       <c r="C20" t="n">
-        <v>0.04979291726953838</v>
+        <v>0.04979214122466389</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1108132112062678</v>
+        <v>-0.1105326497525669</v>
       </c>
       <c r="E20" t="n">
-        <v>0.08437143786068765</v>
+        <v>0.08464895727437975</v>
       </c>
       <c r="F20" t="n">
-        <v>0.790610896025791</v>
+        <v>0.7949274527428574</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1966,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.004335437062310145</v>
+        <v>0.004450654511219905</v>
       </c>
       <c r="C21" t="n">
-        <v>0.05125049584123829</v>
+        <v>0.05125308284729301</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.09611368897633674</v>
+        <v>-0.09600354196612199</v>
       </c>
       <c r="E21" t="n">
-        <v>0.104784563100957</v>
+        <v>0.1049048509885618</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9325849043145344</v>
+        <v>0.9308012234128813</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1991,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.01158397950368181</v>
+        <v>0.01178950629292761</v>
       </c>
       <c r="C22" t="n">
-        <v>0.05351623953049019</v>
+        <v>0.05351780370106506</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.09330592256409768</v>
+        <v>-0.09310346149284433</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1164738815714613</v>
+        <v>0.1166824740786995</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8286313234472735</v>
+        <v>0.8256442990935547</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +2016,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.04490126550683207</v>
+        <v>0.04500853091113273</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05073590126058455</v>
+        <v>0.05073676871697233</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.05453927368709397</v>
+        <v>-0.05443370846607153</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1443418047007581</v>
+        <v>0.144450770288337</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3761567069305497</v>
+        <v>0.3750256648141884</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2041,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.09277287691209132</v>
+        <v>0.09317839536589113</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0419807494514414</v>
+        <v>0.04199057011256824</v>
       </c>
       <c r="D24" t="n">
-        <v>0.01049211994326654</v>
+        <v>0.01087839025495338</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1750536338809161</v>
+        <v>0.1754784004768289</v>
       </c>
       <c r="F24" t="n">
-        <v>0.02711273375311746</v>
+        <v>0.02648458550495966</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2066,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.03607863560750364</v>
+        <v>0.03623225650076151</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02485846017140063</v>
+        <v>0.02486297432359933</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.01264305103956498</v>
+        <v>-0.01249827772203729</v>
       </c>
       <c r="E25" t="n">
-        <v>0.08480032225457225</v>
+        <v>0.08496279072356031</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1466789605900473</v>
+        <v>0.1450397569591432</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2091,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0144839876832471</v>
+        <v>0.01467109228439217</v>
       </c>
       <c r="C26" t="n">
-        <v>0.02811551845289984</v>
+        <v>0.02811127962746577</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.04062141589110788</v>
+        <v>-0.04042600334477528</v>
       </c>
       <c r="E26" t="n">
-        <v>0.06958939125760209</v>
+        <v>0.06976818791355963</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6064412877410577</v>
+        <v>0.6017445295692657</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2116,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.0330984331668712</v>
+        <v>-0.03310111763713029</v>
       </c>
       <c r="C27" t="n">
-        <v>0.02920935542237534</v>
+        <v>0.02920545388089279</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.09034771780635659</v>
+        <v>-0.0903427553958257</v>
       </c>
       <c r="E27" t="n">
-        <v>0.02415085147261419</v>
+        <v>0.02414052012156513</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2571533936244732</v>
+        <v>0.2570512552489402</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2141,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.01378326527887543</v>
+        <v>-0.01368596077233373</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0296437370093222</v>
+        <v>0.02963823096954</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.07188392218432405</v>
+        <v>-0.07177582603811178</v>
       </c>
       <c r="E28" t="n">
-        <v>0.04431739162657319</v>
+        <v>0.04440390449344432</v>
       </c>
       <c r="F28" t="n">
-        <v>0.641957364197689</v>
+        <v>0.6442483269078483</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2166,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.02693520877969161</v>
+        <v>-0.02682587599480331</v>
       </c>
       <c r="C29" t="n">
-        <v>0.02936902969487703</v>
+        <v>0.02937399338914298</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.08449744924253796</v>
+        <v>-0.08439784511964118</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03062703168315475</v>
+        <v>0.03074609313003458</v>
       </c>
       <c r="F29" t="n">
-        <v>0.359074690426296</v>
+        <v>0.3611097025802047</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2191,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.3982233096578142</v>
+        <v>0.3985398745276547</v>
       </c>
       <c r="C30" t="n">
-        <v>0.03926983810596112</v>
+        <v>0.03933933271771812</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3212558412914118</v>
+        <v>0.3214361992250889</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4751907780242166</v>
+        <v>0.4756435498302204</v>
       </c>
       <c r="F30" t="n">
-        <v>3.645104327879733e-24</v>
+        <v>4.032349524444037e-24</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2189,19 +2216,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.638035829451045</v>
+        <v>1.638429102143954</v>
       </c>
       <c r="C31" t="n">
-        <v>0.04812529240022895</v>
+        <v>0.04812377374195419</v>
       </c>
       <c r="D31" t="n">
-        <v>1.543711989601137</v>
+        <v>1.544108238809569</v>
       </c>
       <c r="E31" t="n">
-        <v>1.732359669300953</v>
+        <v>1.732749965478339</v>
       </c>
       <c r="F31" t="n">
-        <v>6.341968535469546e-254</v>
+        <v>4.628174711716707e-254</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2214,19 +2241,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.001517501047856198</v>
+        <v>-0.001532654351402105</v>
       </c>
       <c r="C32" t="n">
-        <v>0.00159977479550119</v>
+        <v>0.001599885891944219</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.004653002030413462</v>
+        <v>-0.004668373078986514</v>
       </c>
       <c r="E32" t="n">
-        <v>0.001617999934701065</v>
+        <v>0.001603064376182304</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3428385058225965</v>
+        <v>0.3380742102093477</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2239,19 +2266,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.002085975822998772</v>
+        <v>-0.002088076448677741</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001402357375237834</v>
+        <v>0.001402263199247398</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.004834545771919049</v>
+        <v>-0.004836461816048555</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0006625941259215049</v>
+        <v>0.0006603089186930726</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1368885945885599</v>
+        <v>0.1364673619490762</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2264,19 +2291,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.003190404661875355</v>
+        <v>-0.003156716305439272</v>
       </c>
       <c r="C34" t="n">
-        <v>0.004191906749099821</v>
+        <v>0.004191434052020042</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.01140639091666138</v>
+        <v>-0.01137177609097334</v>
       </c>
       <c r="E34" t="n">
-        <v>0.005025581592910674</v>
+        <v>0.005058343480094794</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4466052571656727</v>
+        <v>0.4513687051621504</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2312,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>baseline_manager_efficacy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.001072258730903538</v>
+        <v>0.497700636372266</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001289206013563251</v>
+        <v>0.01226810100606325</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.00145453862433289</v>
+        <v>0.4736556002416824</v>
       </c>
       <c r="E35" t="n">
-        <v>0.003599056086139966</v>
+        <v>0.5217456725028495</v>
       </c>
       <c r="F35" t="n">
-        <v>0.4055668752339284</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2310,23 +2337,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>baseline_manager_efficacy</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.4975842499220143</v>
+        <v>0.001063121985276501</v>
       </c>
       <c r="C36" t="n">
-        <v>0.01226979046800327</v>
+        <v>0.001289385890041369</v>
       </c>
       <c r="D36" t="n">
-        <v>0.473535902506875</v>
+        <v>-0.001464027921378704</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5216325973371535</v>
+        <v>0.003590271891931706</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>0.4096452440067891</v>
       </c>
       <c r="G36" t="n">
         <v>0.05</v>
@@ -2343,7 +2370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2375,13 +2402,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.680600179802939</v>
+        <v>-2.774614073588894</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4771933030981503</v>
+        <v>0.5213956350107523</v>
       </c>
       <c r="D2" t="n">
-        <v>1.938181768273511e-08</v>
+        <v>1.029072958037433e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2391,13 +2418,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02542074333516161</v>
+        <v>-0.02531896946916937</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1002143663033998</v>
+        <v>0.1001870355608945</v>
       </c>
       <c r="D3" t="n">
-        <v>0.79975540801217</v>
+        <v>0.8004868915759117</v>
       </c>
     </row>
     <row r="4">
@@ -2407,13 +2434,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2244463748843409</v>
+        <v>0.2256150601556658</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2335027157442915</v>
+        <v>0.2336513202417125</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3364439424069162</v>
+        <v>0.3342414930584408</v>
       </c>
     </row>
     <row r="5">
@@ -2423,13 +2450,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8155080917228588</v>
+        <v>0.8160827895347565</v>
       </c>
       <c r="C5" t="n">
-        <v>0.173402651392118</v>
+        <v>0.1734116198833068</v>
       </c>
       <c r="D5" t="n">
-        <v>2.563995828054386e-06</v>
+        <v>2.525694832362387e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2439,13 +2466,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03527526670387308</v>
+        <v>0.03622598517976097</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1916882946919544</v>
+        <v>0.1914953081760689</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8539945454713548</v>
+        <v>0.8499562329133767</v>
       </c>
     </row>
     <row r="7">
@@ -2455,13 +2482,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2773648159307716</v>
+        <v>0.2771938342360029</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1901447102133385</v>
+        <v>0.1901314810930082</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1446466431125523</v>
+        <v>0.144866444211752</v>
       </c>
     </row>
     <row r="8">
@@ -2471,13 +2498,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1036811851537241</v>
+        <v>0.1053581304950989</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1952515666982444</v>
+        <v>0.195344266715979</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5954095400432469</v>
+        <v>0.5896481989107898</v>
       </c>
     </row>
     <row r="9">
@@ -2487,13 +2514,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8738774480300985</v>
+        <v>0.8758696511293145</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1695280942409139</v>
+        <v>0.1693371735726044</v>
       </c>
       <c r="D9" t="n">
-        <v>2.539495077342821e-07</v>
+        <v>2.311788629896145e-07</v>
       </c>
     </row>
     <row r="10">
@@ -2503,13 +2530,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.0445652077261707</v>
+        <v>-0.0442746205979466</v>
       </c>
       <c r="C10" t="n">
-        <v>0.260402103171632</v>
+        <v>0.2604040478124695</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8641137091517843</v>
+        <v>0.8649922202201155</v>
       </c>
     </row>
     <row r="11">
@@ -2519,13 +2546,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.2737623724798146</v>
+        <v>-0.2742205061505732</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2787881385465067</v>
+        <v>0.2787689544694698</v>
       </c>
       <c r="D11" t="n">
-        <v>0.326113242387764</v>
+        <v>0.3252710045288605</v>
       </c>
     </row>
     <row r="12">
@@ -2535,13 +2562,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08100487957118148</v>
+        <v>0.08193295015444173</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2596429772097172</v>
+        <v>0.2597818841250339</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7550514391424692</v>
+        <v>0.7524645599189498</v>
       </c>
     </row>
     <row r="13">
@@ -2551,13 +2578,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03917827337461754</v>
+        <v>0.03769699417328277</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2572958805743774</v>
+        <v>0.2573362415649837</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8789745077123743</v>
+        <v>0.8835351721093887</v>
       </c>
     </row>
     <row r="14">
@@ -2567,13 +2594,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.05296103812307935</v>
+        <v>-0.05102687086134968</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2610089865588724</v>
+        <v>0.2608488036216079</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8392062624375534</v>
+        <v>0.8449087216020078</v>
       </c>
     </row>
     <row r="15">
@@ -2583,13 +2610,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1181322726534161</v>
+        <v>0.1194505179052277</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2572294350577187</v>
+        <v>0.2572736242808299</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6460556128984086</v>
+        <v>0.6424373510261985</v>
       </c>
     </row>
     <row r="16">
@@ -2599,13 +2626,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.004000986240379481</v>
+        <v>-0.00339452099980482</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2383903410311192</v>
+        <v>0.2383941217340669</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9866094604655132</v>
+        <v>0.9886392149415395</v>
       </c>
     </row>
     <row r="17">
@@ -2615,13 +2642,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1057185310395306</v>
+        <v>0.105173768000375</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2543340222421759</v>
+        <v>0.2544989159147916</v>
       </c>
       <c r="D17" t="n">
-        <v>0.677652912256731</v>
+        <v>0.679417439629268</v>
       </c>
     </row>
     <row r="18">
@@ -2631,13 +2658,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1377694895733254</v>
+        <v>-0.1377738518166142</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2636874203313636</v>
+        <v>0.2637734916431452</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6013412201546282</v>
+        <v>0.6014483864186209</v>
       </c>
     </row>
     <row r="19">
@@ -2647,13 +2674,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02557154094223237</v>
+        <v>-0.02393490642264785</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2527597901538116</v>
+        <v>0.2529805715426143</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9194160355966677</v>
+        <v>0.9246233049950203</v>
       </c>
     </row>
     <row r="20">
@@ -2663,13 +2690,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.07344622569376411</v>
+        <v>-0.07301273583929982</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2674578609541021</v>
+        <v>0.2675190900686553</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7836169672222787</v>
+        <v>0.7849106151948622</v>
       </c>
     </row>
     <row r="21">
@@ -2679,13 +2706,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2063167170305062</v>
+        <v>0.2069135147918238</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2442896532450728</v>
+        <v>0.24428709892913</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3983578134719854</v>
+        <v>0.3969897777610724</v>
       </c>
     </row>
     <row r="22">
@@ -2695,13 +2722,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1704634573362028</v>
+        <v>-0.1717092932306343</v>
       </c>
       <c r="C22" t="n">
-        <v>0.269674845496591</v>
+        <v>0.2696190828094301</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5273167196806365</v>
+        <v>0.5242168027309894</v>
       </c>
     </row>
     <row r="23">
@@ -2711,13 +2738,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.5008110927334755</v>
+        <v>-0.5023322926397003</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2870672180445716</v>
+        <v>0.2872431741192609</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0810583897517186</v>
+        <v>0.08032473613005453</v>
       </c>
     </row>
     <row r="24">
@@ -2727,13 +2754,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9366864721074268</v>
+        <v>0.9363452786511914</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1483430409733375</v>
+        <v>0.1483102369545482</v>
       </c>
       <c r="D24" t="n">
-        <v>2.713396260923871e-10</v>
+        <v>2.72929944135029e-10</v>
       </c>
     </row>
     <row r="25">
@@ -2743,13 +2770,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5776106069409677</v>
+        <v>-0.5780513937211161</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1143619392421806</v>
+        <v>0.1144316984848933</v>
       </c>
       <c r="D25" t="n">
-        <v>4.401383208103854e-07</v>
+        <v>4.383605797803349e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2759,13 +2786,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2373161448441742</v>
+        <v>0.2362077053959268</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1503781926377481</v>
+        <v>0.1504768607120736</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1145360411757815</v>
+        <v>0.1164784602604653</v>
       </c>
     </row>
     <row r="27">
@@ -2775,13 +2802,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04350476117998643</v>
+        <v>-0.04595559996241684</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1611879340386415</v>
+        <v>0.1616567014228949</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7872365295400221</v>
+        <v>0.7761966040079398</v>
       </c>
     </row>
     <row r="28">
@@ -2791,13 +2818,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.07514354096975739</v>
+        <v>-0.0760596782382283</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1613683918223571</v>
+        <v>0.1614891401822261</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6414556246120158</v>
+        <v>0.6376482824383396</v>
       </c>
     </row>
     <row r="29">
@@ -2807,13 +2834,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09749293462742094</v>
+        <v>0.09626986426402336</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1543265796290169</v>
+        <v>0.1543844601757256</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5275624553510021</v>
+        <v>0.532908543609379</v>
       </c>
     </row>
     <row r="30">
@@ -2823,13 +2850,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2280638724458788</v>
+        <v>0.3248984989766643</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1146565719927948</v>
+        <v>0.2612255249732426</v>
       </c>
       <c r="D30" t="n">
-        <v>0.04668969945129902</v>
+        <v>0.2135926414117545</v>
       </c>
     </row>
     <row r="31">
@@ -2839,13 +2866,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.005012017390962181</v>
+        <v>-0.005017911290030882</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008304876992454899</v>
+        <v>0.008305443072288938</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5461741835341518</v>
+        <v>0.5457296836910626</v>
       </c>
     </row>
     <row r="32">
@@ -2855,13 +2882,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.002418133412192865</v>
+        <v>-0.002426755242405134</v>
       </c>
       <c r="C32" t="n">
-        <v>0.007135781003458533</v>
+        <v>0.007136997489227805</v>
       </c>
       <c r="D32" t="n">
-        <v>0.7347043603418282</v>
+        <v>0.7338379468830427</v>
       </c>
     </row>
     <row r="33">
@@ -2871,29 +2898,45 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.004129656026475429</v>
+        <v>-0.004305141260627514</v>
       </c>
       <c r="C33" t="n">
-        <v>0.02222260881033176</v>
+        <v>0.02221655124176766</v>
       </c>
       <c r="D33" t="n">
-        <v>0.8525770672961277</v>
+        <v>0.8463475148043504</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>baseline_manager_efficacy</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.02937091471947247</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.06892977188933398</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.6700356258910078</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>tot_span_of_control</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>0.006335499136474494</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0.006871422968197173</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0.3565249957666431</v>
+      <c r="B35" t="n">
+        <v>0.006290302487114359</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.006868867616884194</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.3597875728110747</v>
       </c>
     </row>
   </sheetData>
